--- a/sheets/Libetee_8月シミュレーション_公式確定版.xlsx
+++ b/sheets/Libetee_8月シミュレーション_公式確定版.xlsx
@@ -20,12 +20,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="0.00&quot;%&quot;"/>
     <numFmt numFmtId="165" formatCode="¥#,##0"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
-    <numFmt numFmtId="167" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="168" formatCode="m/d(aaa)"/>
+    <numFmt numFmtId="167" formatCode="m/d(aaa)"/>
   </numFmts>
   <fonts count="8">
     <font>
@@ -155,7 +154,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -261,22 +260,52 @@
     <xf numFmtId="165" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -932,6 +961,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -994,8 +1024,8 @@
       <c r="B5" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="C5" s="6" t="n">
-        <v>0.7307402038884963</v>
+      <c r="C5" s="59" t="n">
+        <v>0.007307402038884962</v>
       </c>
       <c r="D5" s="7" t="n">
         <v>13048</v>
@@ -1028,8 +1058,8 @@
       <c r="B6" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="C6" s="11" t="n">
-        <v>0.6999776602874377</v>
+      <c r="C6" s="60" t="n">
+        <v>0.006999776602874377</v>
       </c>
       <c r="D6" s="12" t="n">
         <v>8765</v>
@@ -1062,8 +1092,8 @@
       <c r="B7" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="C7" s="16" t="n">
-        <v>0.3378378378378378</v>
+      <c r="C7" s="61" t="n">
+        <v>0.003378378378378378</v>
       </c>
       <c r="D7" s="17" t="n">
         <v>27905</v>
@@ -1096,8 +1126,8 @@
       <c r="B8" s="20" t="n">
         <v>7</v>
       </c>
-      <c r="C8" s="21" t="n">
-        <v>0.3021880463286714</v>
+      <c r="C8" s="62" t="n">
+        <v>0.003021880463286714</v>
       </c>
       <c r="D8" s="22" t="n">
         <v>15334</v>
@@ -1130,8 +1160,8 @@
       <c r="B9" s="25" t="n">
         <v>17</v>
       </c>
-      <c r="C9" s="26" t="n">
-        <v>0.372457195612264</v>
+      <c r="C9" s="63" t="n">
+        <v>0.00372457195612264</v>
       </c>
       <c r="D9" s="27" t="n">
         <v>10958</v>
@@ -1177,6 +1207,7 @@
         <v>59630091</v>
       </c>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="31" t="inlineStr">
         <is>
@@ -1212,6 +1243,7 @@
         </is>
       </c>
     </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
@@ -1279,6 +1311,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -1363,6 +1396,8 @@
         <v>1</v>
       </c>
     </row>
+    <row r="8"/>
+    <row r="9"/>
     <row r="10">
       <c r="A10" s="31" t="inlineStr">
         <is>
@@ -1551,6 +1586,9 @@
         <v>59630091</v>
       </c>
     </row>
+    <row r="5"/>
+    <row r="6"/>
+    <row r="7"/>
     <row r="8">
       <c r="H8" t="inlineStr">
         <is>
@@ -1666,6 +1704,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
@@ -1714,7 +1753,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="53" t="n">
+      <c r="A4" s="64" t="n">
         <v>46235</v>
       </c>
       <c r="B4" s="15" t="inlineStr">
@@ -1745,7 +1784,7 @@
       <c r="I4" s="14" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="54" t="n">
+      <c r="A5" s="65" t="n">
         <v>46236</v>
       </c>
       <c r="B5" s="25" t="inlineStr">
@@ -1776,7 +1815,7 @@
       <c r="I5" s="24" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="54" t="n">
+      <c r="A6" s="65" t="n">
         <v>46237</v>
       </c>
       <c r="B6" s="25" t="inlineStr">
@@ -1807,7 +1846,7 @@
       <c r="I6" s="24" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="55" t="n">
+      <c r="A7" s="66" t="n">
         <v>46238</v>
       </c>
       <c r="B7" s="20" t="inlineStr">
@@ -1842,7 +1881,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="56" t="n">
+      <c r="A8" s="67" t="n">
         <v>46239</v>
       </c>
       <c r="B8" s="5" t="inlineStr">
@@ -1877,7 +1916,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="55" t="n">
+      <c r="A9" s="66" t="n">
         <v>46240</v>
       </c>
       <c r="B9" s="20" t="inlineStr">
@@ -1908,7 +1947,7 @@
       <c r="I9" s="19" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="55" t="n">
+      <c r="A10" s="66" t="n">
         <v>46241</v>
       </c>
       <c r="B10" s="20" t="inlineStr">
@@ -1939,7 +1978,7 @@
       <c r="I10" s="19" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="55" t="n">
+      <c r="A11" s="66" t="n">
         <v>46242</v>
       </c>
       <c r="B11" s="20" t="inlineStr">
@@ -1970,7 +2009,7 @@
       <c r="I11" s="19" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="55" t="n">
+      <c r="A12" s="66" t="n">
         <v>46243</v>
       </c>
       <c r="B12" s="20" t="inlineStr">
@@ -2001,7 +2040,7 @@
       <c r="I12" s="19" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="56" t="n">
+      <c r="A13" s="67" t="n">
         <v>46244</v>
       </c>
       <c r="B13" s="5" t="inlineStr">
@@ -2036,7 +2075,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="54" t="n">
+      <c r="A14" s="65" t="n">
         <v>46245</v>
       </c>
       <c r="B14" s="25" t="inlineStr">
@@ -2071,7 +2110,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="54" t="n">
+      <c r="A15" s="65" t="n">
         <v>46246</v>
       </c>
       <c r="B15" s="25" t="inlineStr">
@@ -2102,7 +2141,7 @@
       <c r="I15" s="24" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="54" t="n">
+      <c r="A16" s="65" t="n">
         <v>46247</v>
       </c>
       <c r="B16" s="25" t="inlineStr">
@@ -2133,7 +2172,7 @@
       <c r="I16" s="24" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="54" t="n">
+      <c r="A17" s="65" t="n">
         <v>46248</v>
       </c>
       <c r="B17" s="25" t="inlineStr">
@@ -2164,7 +2203,7 @@
       <c r="I17" s="24" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="57" t="n">
+      <c r="A18" s="68" t="n">
         <v>46249</v>
       </c>
       <c r="B18" s="10" t="inlineStr">
@@ -2195,7 +2234,7 @@
       <c r="I18" s="9" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="54" t="n">
+      <c r="A19" s="65" t="n">
         <v>46250</v>
       </c>
       <c r="B19" s="25" t="inlineStr">
@@ -2226,7 +2265,7 @@
       <c r="I19" s="24" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="54" t="n">
+      <c r="A20" s="65" t="n">
         <v>46251</v>
       </c>
       <c r="B20" s="25" t="inlineStr">
@@ -2257,7 +2296,7 @@
       <c r="I20" s="24" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="54" t="n">
+      <c r="A21" s="65" t="n">
         <v>46252</v>
       </c>
       <c r="B21" s="25" t="inlineStr">
@@ -2288,7 +2327,7 @@
       <c r="I21" s="24" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="54" t="n">
+      <c r="A22" s="65" t="n">
         <v>46253</v>
       </c>
       <c r="B22" s="25" t="inlineStr">
@@ -2319,7 +2358,7 @@
       <c r="I22" s="24" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="57" t="n">
+      <c r="A23" s="68" t="n">
         <v>46254</v>
       </c>
       <c r="B23" s="10" t="inlineStr">
@@ -2350,7 +2389,7 @@
       <c r="I23" s="9" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="54" t="n">
+      <c r="A24" s="65" t="n">
         <v>46255</v>
       </c>
       <c r="B24" s="25" t="inlineStr">
@@ -2381,7 +2420,7 @@
       <c r="I24" s="24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="54" t="n">
+      <c r="A25" s="65" t="n">
         <v>46256</v>
       </c>
       <c r="B25" s="25" t="inlineStr">
@@ -2412,7 +2451,7 @@
       <c r="I25" s="24" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="54" t="n">
+      <c r="A26" s="65" t="n">
         <v>46257</v>
       </c>
       <c r="B26" s="25" t="inlineStr">
@@ -2443,7 +2482,7 @@
       <c r="I26" s="24" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="55" t="n">
+      <c r="A27" s="66" t="n">
         <v>46258</v>
       </c>
       <c r="B27" s="20" t="inlineStr">
@@ -2478,7 +2517,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="56" t="n">
+      <c r="A28" s="67" t="n">
         <v>46259</v>
       </c>
       <c r="B28" s="5" t="inlineStr">
@@ -2513,7 +2552,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="55" t="n">
+      <c r="A29" s="66" t="n">
         <v>46260</v>
       </c>
       <c r="B29" s="20" t="inlineStr">
@@ -2544,7 +2583,7 @@
       <c r="I29" s="19" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="54" t="n">
+      <c r="A30" s="65" t="n">
         <v>46261</v>
       </c>
       <c r="B30" s="25" t="inlineStr">
@@ -2579,7 +2618,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="54" t="n">
+      <c r="A31" s="65" t="n">
         <v>46262</v>
       </c>
       <c r="B31" s="25" t="inlineStr">
@@ -2610,7 +2649,7 @@
       <c r="I31" s="24" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="54" t="n">
+      <c r="A32" s="65" t="n">
         <v>46263</v>
       </c>
       <c r="B32" s="25" t="inlineStr">
@@ -2641,7 +2680,7 @@
       <c r="I32" s="24" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="57" t="n">
+      <c r="A33" s="68" t="n">
         <v>46264</v>
       </c>
       <c r="B33" s="10" t="inlineStr">
@@ -2672,7 +2711,7 @@
       <c r="I33" s="9" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="54" t="n">
+      <c r="A34" s="65" t="n">
         <v>46265</v>
       </c>
       <c r="B34" s="25" t="inlineStr">

--- a/sheets/Libetee_8月シミュレーション_公式確定版.xlsx
+++ b/sheets/Libetee_8月シミュレーション_公式確定版.xlsx
@@ -1753,8 +1753,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="64" t="n">
-        <v>46235</v>
+      <c r="A4" s="15" t="inlineStr">
+        <is>
+          <t>8/1(土)</t>
+        </is>
       </c>
       <c r="B4" s="15" t="inlineStr">
         <is>
@@ -1784,8 +1786,10 @@
       <c r="I4" s="14" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="65" t="n">
-        <v>46236</v>
+      <c r="A5" s="25" t="inlineStr">
+        <is>
+          <t>8/2(日)</t>
+        </is>
       </c>
       <c r="B5" s="25" t="inlineStr">
         <is>
@@ -1815,8 +1819,10 @@
       <c r="I5" s="24" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="65" t="n">
-        <v>46237</v>
+      <c r="A6" s="25" t="inlineStr">
+        <is>
+          <t>8/3(月)</t>
+        </is>
       </c>
       <c r="B6" s="25" t="inlineStr">
         <is>
@@ -1846,8 +1852,10 @@
       <c r="I6" s="24" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="66" t="n">
-        <v>46238</v>
+      <c r="A7" s="20" t="inlineStr">
+        <is>
+          <t>8/4(火)</t>
+        </is>
       </c>
       <c r="B7" s="20" t="inlineStr">
         <is>
@@ -1881,8 +1889,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="67" t="n">
-        <v>46239</v>
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>8/5(水)</t>
+        </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
@@ -1916,8 +1926,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="66" t="n">
-        <v>46240</v>
+      <c r="A9" s="20" t="inlineStr">
+        <is>
+          <t>8/6(木)</t>
+        </is>
       </c>
       <c r="B9" s="20" t="inlineStr">
         <is>
@@ -1947,8 +1959,10 @@
       <c r="I9" s="19" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="66" t="n">
-        <v>46241</v>
+      <c r="A10" s="20" t="inlineStr">
+        <is>
+          <t>8/7(金)</t>
+        </is>
       </c>
       <c r="B10" s="20" t="inlineStr">
         <is>
@@ -1978,8 +1992,10 @@
       <c r="I10" s="19" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="66" t="n">
-        <v>46242</v>
+      <c r="A11" s="20" t="inlineStr">
+        <is>
+          <t>8/8(土)</t>
+        </is>
       </c>
       <c r="B11" s="20" t="inlineStr">
         <is>
@@ -2009,8 +2025,10 @@
       <c r="I11" s="19" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="66" t="n">
-        <v>46243</v>
+      <c r="A12" s="20" t="inlineStr">
+        <is>
+          <t>8/9(日)</t>
+        </is>
       </c>
       <c r="B12" s="20" t="inlineStr">
         <is>
@@ -2040,8 +2058,10 @@
       <c r="I12" s="19" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="67" t="n">
-        <v>46244</v>
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>8/10(月)</t>
+        </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
@@ -2075,8 +2095,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="65" t="n">
-        <v>46245</v>
+      <c r="A14" s="25" t="inlineStr">
+        <is>
+          <t>8/11(火)</t>
+        </is>
       </c>
       <c r="B14" s="25" t="inlineStr">
         <is>
@@ -2110,8 +2132,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="65" t="n">
-        <v>46246</v>
+      <c r="A15" s="25" t="inlineStr">
+        <is>
+          <t>8/12(水)</t>
+        </is>
       </c>
       <c r="B15" s="25" t="inlineStr">
         <is>
@@ -2141,8 +2165,10 @@
       <c r="I15" s="24" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="65" t="n">
-        <v>46247</v>
+      <c r="A16" s="25" t="inlineStr">
+        <is>
+          <t>8/13(木)</t>
+        </is>
       </c>
       <c r="B16" s="25" t="inlineStr">
         <is>
@@ -2172,8 +2198,10 @@
       <c r="I16" s="24" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="65" t="n">
-        <v>46248</v>
+      <c r="A17" s="25" t="inlineStr">
+        <is>
+          <t>8/14(金)</t>
+        </is>
       </c>
       <c r="B17" s="25" t="inlineStr">
         <is>
@@ -2203,8 +2231,10 @@
       <c r="I17" s="24" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="68" t="n">
-        <v>46249</v>
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>8/15(土)</t>
+        </is>
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
@@ -2234,8 +2264,10 @@
       <c r="I18" s="9" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="65" t="n">
-        <v>46250</v>
+      <c r="A19" s="25" t="inlineStr">
+        <is>
+          <t>8/16(日)</t>
+        </is>
       </c>
       <c r="B19" s="25" t="inlineStr">
         <is>
@@ -2265,8 +2297,10 @@
       <c r="I19" s="24" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="65" t="n">
-        <v>46251</v>
+      <c r="A20" s="25" t="inlineStr">
+        <is>
+          <t>8/17(月)</t>
+        </is>
       </c>
       <c r="B20" s="25" t="inlineStr">
         <is>
@@ -2296,8 +2330,10 @@
       <c r="I20" s="24" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="65" t="n">
-        <v>46252</v>
+      <c r="A21" s="25" t="inlineStr">
+        <is>
+          <t>8/18(火)</t>
+        </is>
       </c>
       <c r="B21" s="25" t="inlineStr">
         <is>
@@ -2327,8 +2363,10 @@
       <c r="I21" s="24" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="65" t="n">
-        <v>46253</v>
+      <c r="A22" s="25" t="inlineStr">
+        <is>
+          <t>8/19(水)</t>
+        </is>
       </c>
       <c r="B22" s="25" t="inlineStr">
         <is>
@@ -2358,8 +2396,10 @@
       <c r="I22" s="24" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="68" t="n">
-        <v>46254</v>
+      <c r="A23" s="10" t="inlineStr">
+        <is>
+          <t>8/20(木)</t>
+        </is>
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
@@ -2389,8 +2429,10 @@
       <c r="I23" s="9" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="65" t="n">
-        <v>46255</v>
+      <c r="A24" s="25" t="inlineStr">
+        <is>
+          <t>8/21(金)</t>
+        </is>
       </c>
       <c r="B24" s="25" t="inlineStr">
         <is>
@@ -2420,8 +2462,10 @@
       <c r="I24" s="24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="65" t="n">
-        <v>46256</v>
+      <c r="A25" s="25" t="inlineStr">
+        <is>
+          <t>8/22(土)</t>
+        </is>
       </c>
       <c r="B25" s="25" t="inlineStr">
         <is>
@@ -2451,8 +2495,10 @@
       <c r="I25" s="24" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="65" t="n">
-        <v>46257</v>
+      <c r="A26" s="25" t="inlineStr">
+        <is>
+          <t>8/23(日)</t>
+        </is>
       </c>
       <c r="B26" s="25" t="inlineStr">
         <is>
@@ -2482,8 +2528,10 @@
       <c r="I26" s="24" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="66" t="n">
-        <v>46258</v>
+      <c r="A27" s="20" t="inlineStr">
+        <is>
+          <t>8/24(月)</t>
+        </is>
       </c>
       <c r="B27" s="20" t="inlineStr">
         <is>
@@ -2517,8 +2565,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="67" t="n">
-        <v>46259</v>
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>8/25(火)</t>
+        </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
@@ -2552,8 +2602,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="66" t="n">
-        <v>46260</v>
+      <c r="A29" s="20" t="inlineStr">
+        <is>
+          <t>8/26(水)</t>
+        </is>
       </c>
       <c r="B29" s="20" t="inlineStr">
         <is>
@@ -2583,8 +2635,10 @@
       <c r="I29" s="19" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="65" t="n">
-        <v>46261</v>
+      <c r="A30" s="25" t="inlineStr">
+        <is>
+          <t>8/27(木)</t>
+        </is>
       </c>
       <c r="B30" s="25" t="inlineStr">
         <is>
@@ -2618,8 +2672,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="65" t="n">
-        <v>46262</v>
+      <c r="A31" s="25" t="inlineStr">
+        <is>
+          <t>8/28(金)</t>
+        </is>
       </c>
       <c r="B31" s="25" t="inlineStr">
         <is>
@@ -2649,8 +2705,10 @@
       <c r="I31" s="24" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="65" t="n">
-        <v>46263</v>
+      <c r="A32" s="25" t="inlineStr">
+        <is>
+          <t>8/29(土)</t>
+        </is>
       </c>
       <c r="B32" s="25" t="inlineStr">
         <is>
@@ -2680,8 +2738,10 @@
       <c r="I32" s="24" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="68" t="n">
-        <v>46264</v>
+      <c r="A33" s="10" t="inlineStr">
+        <is>
+          <t>8/30(日)</t>
+        </is>
       </c>
       <c r="B33" s="10" t="inlineStr">
         <is>
@@ -2711,8 +2771,10 @@
       <c r="I33" s="9" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="65" t="n">
-        <v>46265</v>
+      <c r="A34" s="25" t="inlineStr">
+        <is>
+          <t>8/31(月)</t>
+        </is>
       </c>
       <c r="B34" s="25" t="inlineStr">
         <is>

--- a/sheets/Libetee_8月シミュレーション_公式確定版.xlsx
+++ b/sheets/Libetee_8月シミュレーション_公式確定版.xlsx
@@ -12,6 +12,7 @@
     <sheet name="グラフ" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="日別明細" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="前提と検算" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="用語解説" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,13 +21,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="0.00&quot;%&quot;"/>
     <numFmt numFmtId="165" formatCode="¥#,##0"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
     <numFmt numFmtId="167" formatCode="m/d(aaa)"/>
+    <numFmt numFmtId="168" formatCode="0.0&quot;倍&quot;"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -68,6 +70,11 @@
     </font>
     <font>
       <name val="Arial"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="14"/>
     </font>
   </fonts>
   <fills count="12">
@@ -154,7 +161,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="69">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -306,6 +313,25 @@
     <xf numFmtId="167" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -961,7 +987,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -1207,7 +1232,6 @@
         <v>59630091</v>
       </c>
     </row>
-    <row r="11"/>
     <row r="12">
       <c r="A12" s="31" t="inlineStr">
         <is>
@@ -1243,7 +1267,6 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
@@ -1311,7 +1334,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -1396,8 +1418,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8"/>
-    <row r="9"/>
     <row r="10">
       <c r="A10" s="31" t="inlineStr">
         <is>
@@ -1586,9 +1606,6 @@
         <v>59630091</v>
       </c>
     </row>
-    <row r="5"/>
-    <row r="6"/>
-    <row r="7"/>
     <row r="8">
       <c r="H8" t="inlineStr">
         <is>
@@ -1704,7 +1721,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
@@ -2923,4 +2939,248 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="69" t="inlineStr">
+        <is>
+          <t>用語解説：1アクセス価値</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="70" t="inlineStr">
+        <is>
+          <t>定義</t>
+        </is>
+      </c>
+      <c r="B3" s="71" t="inlineStr">
+        <is>
+          <t>お客さん1人がページに来たとき、平均していくら売上になるか</t>
+        </is>
+      </c>
+      <c r="C3" s="72" t="n"/>
+      <c r="D3" s="72" t="n"/>
+      <c r="E3" s="72" t="n"/>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="70" t="inlineStr">
+        <is>
+          <t>計算式</t>
+        </is>
+      </c>
+      <c r="B4" s="71" t="inlineStr">
+        <is>
+          <t>1アクセス価値 ＝ 転換率 × 客単価</t>
+        </is>
+      </c>
+      <c r="C4" s="72" t="n"/>
+      <c r="D4" s="72" t="n"/>
+      <c r="E4" s="72" t="n"/>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="70" t="inlineStr">
+        <is>
+          <t>例（かぶり日・7月実績）</t>
+        </is>
+      </c>
+      <c r="B5" s="71" t="inlineStr">
+        <is>
+          <t>転換率0.73% × 客単価¥13,048 ≒ ¥95。1,000人来たら約7人が買い、売上約¥95,000 → 1人あたり¥95</t>
+        </is>
+      </c>
+      <c r="C5" s="72" t="n"/>
+      <c r="D5" s="72" t="n"/>
+      <c r="E5" s="72" t="n"/>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="70" t="inlineStr">
+        <is>
+          <t>使い方①（広告判断）</t>
+        </is>
+      </c>
+      <c r="B6" s="71" t="inlineStr">
+        <is>
+          <t>メタ広告のアクセス単価(約¥12)と比べる。¥12で1人連れてきて、その日の価値が¥95なら8倍で返る計算</t>
+        </is>
+      </c>
+      <c r="C6" s="72" t="n"/>
+      <c r="D6" s="72" t="n"/>
+      <c r="E6" s="72" t="n"/>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="70" t="inlineStr">
+        <is>
+          <t>使い方②（増額試算）</t>
+        </is>
+      </c>
+      <c r="B7" s="71" t="inlineStr">
+        <is>
+          <t>追加売上 ＝ 増やすアクセス数 × 1アクセス価値。転換率×0.8のシナリオは価値を2割引きで見積もったもの</t>
+        </is>
+      </c>
+      <c r="C7" s="72" t="n"/>
+      <c r="D7" s="72" t="n"/>
+      <c r="E7" s="72" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="31" t="inlineStr">
+        <is>
+          <t>セグメント別 1アクセス価値（7月公式実績・店舗全体）</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="73" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="B10" s="73" t="inlineStr">
+        <is>
+          <t>1アクセス価値</t>
+        </is>
+      </c>
+      <c r="C10" s="73" t="inlineStr">
+        <is>
+          <t>広告単価(メタ)</t>
+        </is>
+      </c>
+      <c r="D10" s="73" t="inlineStr">
+        <is>
+          <t>倍率</t>
+        </is>
+      </c>
+      <c r="E10" s="73" t="inlineStr">
+        <is>
+          <t>読み方</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="43" t="inlineStr">
+        <is>
+          <t>かぶり日（イベント×5と0）</t>
+        </is>
+      </c>
+      <c r="B11" s="44" t="n">
+        <v>95</v>
+      </c>
+      <c r="C11" s="44" t="n">
+        <v>12</v>
+      </c>
+      <c r="D11" s="74" t="n">
+        <v>7.916666666666667</v>
+      </c>
+      <c r="E11" s="75" t="inlineStr">
+        <is>
+          <t>¥12仕入→¥95売上。最優先で広告を張る日</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="47" t="inlineStr">
+        <is>
+          <t>ワンダフルデー</t>
+        </is>
+      </c>
+      <c r="B12" s="48" t="n">
+        <v>94</v>
+      </c>
+      <c r="C12" s="48" t="n">
+        <v>12</v>
+      </c>
+      <c r="D12" s="76" t="n">
+        <v>7.833333333333333</v>
+      </c>
+      <c r="E12" s="77" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="45" t="inlineStr">
+        <is>
+          <t>5と0のつく日（単独）</t>
+        </is>
+      </c>
+      <c r="B13" s="46" t="n">
+        <v>61</v>
+      </c>
+      <c r="C13" s="46" t="n">
+        <v>12</v>
+      </c>
+      <c r="D13" s="78" t="n">
+        <v>5.083333333333333</v>
+      </c>
+      <c r="E13" s="79" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="49" t="inlineStr">
+        <is>
+          <t>マラソン通常</t>
+        </is>
+      </c>
+      <c r="B14" s="50" t="n">
+        <v>46</v>
+      </c>
+      <c r="C14" s="50" t="n">
+        <v>12</v>
+      </c>
+      <c r="D14" s="80" t="n">
+        <v>3.833333333333333</v>
+      </c>
+      <c r="E14" s="81" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="51" t="inlineStr">
+        <is>
+          <t>平日</t>
+        </is>
+      </c>
+      <c r="B15" s="52" t="n">
+        <v>41</v>
+      </c>
+      <c r="C15" s="52" t="n">
+        <v>12</v>
+      </c>
+      <c r="D15" s="82" t="n">
+        <v>3.416666666666667</v>
+      </c>
+      <c r="E15" s="83" t="inlineStr">
+        <is>
+          <t>それでも3.4倍。広告を切らない理由</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>※スーツケースのみの価値は別掲（平日¥45／かぶり日¥110）。転換率・客単価は2026年7月実績（公式カレンダー分類）。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="B7:E7"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="B5:E5"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/sheets/Libetee_8月シミュレーション_公式確定版.xlsx
+++ b/sheets/Libetee_8月シミュレーション_公式確定版.xlsx
@@ -135,7 +135,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -156,6 +156,50 @@
       <bottom style="thin">
         <color rgb="00BFBFBF"/>
       </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -2947,20 +2991,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="69" t="inlineStr">
         <is>
-          <t>用語解説：1アクセス価値</t>
+          <t>用語解説：1アクセス価値 ／ アクセス単価の前提</t>
         </is>
       </c>
     </row>
@@ -3017,7 +3061,7 @@
       </c>
       <c r="B6" s="71" t="inlineStr">
         <is>
-          <t>メタ広告のアクセス単価(約¥12)と比べる。¥12で1人連れてきて、その日の価値が¥95なら8倍で返る計算</t>
+          <t>アクセス単価と比べる。¥10で1人連れてきて、その日の価値が¥95なら9.5倍で返る計算</t>
         </is>
       </c>
       <c r="C6" s="72" t="n"/>
@@ -3039,142 +3083,158 @@
       <c r="D7" s="72" t="n"/>
       <c r="E7" s="72" t="n"/>
     </row>
-    <row r="9">
-      <c r="A9" s="31" t="inlineStr">
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="70" t="inlineStr">
+        <is>
+          <t>★アクセス単価の統一前提</t>
+        </is>
+      </c>
+      <c r="B8" s="71" t="inlineStr">
+        <is>
+          <t>スーツケース ¥10/アクセス ／ ハンディファン ¥8/アクセス（社長指定・全シート共通）</t>
+        </is>
+      </c>
+      <c r="C8" s="72" t="n"/>
+      <c r="D8" s="72" t="n"/>
+      <c r="E8" s="72" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="31" t="inlineStr">
         <is>
           <t>セグメント別 1アクセス価値（7月公式実績・店舗全体）</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="73" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="73" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B10" s="73" t="inlineStr">
+      <c r="B11" s="73" t="inlineStr">
         <is>
           <t>1アクセス価値</t>
         </is>
       </c>
-      <c r="C10" s="73" t="inlineStr">
-        <is>
-          <t>広告単価(メタ)</t>
-        </is>
-      </c>
-      <c r="D10" s="73" t="inlineStr">
+      <c r="C11" s="73" t="inlineStr">
+        <is>
+          <t>SC単価</t>
+        </is>
+      </c>
+      <c r="D11" s="73" t="inlineStr">
         <is>
           <t>倍率</t>
         </is>
       </c>
-      <c r="E10" s="73" t="inlineStr">
+      <c r="E11" s="73" t="inlineStr">
         <is>
           <t>読み方</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="43" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="43" t="inlineStr">
         <is>
           <t>かぶり日（イベント×5と0）</t>
         </is>
       </c>
-      <c r="B11" s="44" t="n">
+      <c r="B12" s="44" t="n">
         <v>95</v>
       </c>
-      <c r="C11" s="44" t="n">
-        <v>12</v>
-      </c>
-      <c r="D11" s="74" t="n">
-        <v>7.916666666666667</v>
-      </c>
-      <c r="E11" s="75" t="inlineStr">
-        <is>
-          <t>¥12仕入→¥95売上。最優先で広告を張る日</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="47" t="inlineStr">
+      <c r="C12" s="44" t="n">
+        <v>10</v>
+      </c>
+      <c r="D12" s="74" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="E12" s="75" t="inlineStr">
+        <is>
+          <t>¥10仕入→¥95売上。最優先で広告を張る日</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="47" t="inlineStr">
         <is>
           <t>ワンダフルデー</t>
         </is>
       </c>
-      <c r="B12" s="48" t="n">
+      <c r="B13" s="48" t="n">
         <v>94</v>
       </c>
-      <c r="C12" s="48" t="n">
-        <v>12</v>
-      </c>
-      <c r="D12" s="76" t="n">
-        <v>7.833333333333333</v>
-      </c>
-      <c r="E12" s="77" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="45" t="inlineStr">
+      <c r="C13" s="48" t="n">
+        <v>10</v>
+      </c>
+      <c r="D13" s="76" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="E13" s="77" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="45" t="inlineStr">
         <is>
           <t>5と0のつく日（単独）</t>
         </is>
       </c>
-      <c r="B13" s="46" t="n">
+      <c r="B14" s="46" t="n">
         <v>61</v>
       </c>
-      <c r="C13" s="46" t="n">
-        <v>12</v>
-      </c>
-      <c r="D13" s="78" t="n">
-        <v>5.083333333333333</v>
-      </c>
-      <c r="E13" s="79" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="49" t="inlineStr">
+      <c r="C14" s="46" t="n">
+        <v>10</v>
+      </c>
+      <c r="D14" s="78" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="E14" s="79" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="49" t="inlineStr">
         <is>
           <t>マラソン通常</t>
         </is>
       </c>
-      <c r="B14" s="50" t="n">
+      <c r="B15" s="50" t="n">
         <v>46</v>
       </c>
-      <c r="C14" s="50" t="n">
-        <v>12</v>
-      </c>
-      <c r="D14" s="80" t="n">
-        <v>3.833333333333333</v>
-      </c>
-      <c r="E14" s="81" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="51" t="inlineStr">
+      <c r="C15" s="50" t="n">
+        <v>10</v>
+      </c>
+      <c r="D15" s="80" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="E15" s="81" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="51" t="inlineStr">
         <is>
           <t>平日</t>
         </is>
       </c>
-      <c r="B15" s="52" t="n">
+      <c r="B16" s="52" t="n">
         <v>41</v>
       </c>
-      <c r="C15" s="52" t="n">
-        <v>12</v>
-      </c>
-      <c r="D15" s="82" t="n">
-        <v>3.416666666666667</v>
-      </c>
-      <c r="E15" s="83" t="inlineStr">
-        <is>
-          <t>それでも3.4倍。広告を切らない理由</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>※スーツケースのみの価値は別掲（平日¥45／かぶり日¥110）。転換率・客単価は2026年7月実績（公式カレンダー分類）。</t>
+      <c r="C16" s="52" t="n">
+        <v>10</v>
+      </c>
+      <c r="D16" s="82" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="E16" s="83" t="inlineStr">
+        <is>
+          <t>それでも4.1倍。広告を切らない理由</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>※スーツケースのみの価値：平日¥45／かぶり日¥110。ハンディファンの広告費は¥8/アクセス（据え置き）。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
+    <mergeCell ref="B8:E8"/>
     <mergeCell ref="B4:E4"/>
     <mergeCell ref="B6:E6"/>
     <mergeCell ref="B7:E7"/>

--- a/sheets/Libetee_8月シミュレーション_公式確定版.xlsx
+++ b/sheets/Libetee_8月シミュレーション_公式確定版.xlsx
@@ -77,7 +77,7 @@
       <sz val="14"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill/>
     </fill>
@@ -132,6 +132,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00DDEBD8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -205,7 +210,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="84">
+  <cellXfs count="87">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -376,6 +381,15 @@
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -2991,255 +3005,230 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="42" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="69" t="inlineStr">
         <is>
-          <t>用語解説：1アクセス価値 ／ アクセス単価の前提</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="70" t="inlineStr">
-        <is>
-          <t>定義</t>
-        </is>
-      </c>
-      <c r="B3" s="71" t="inlineStr">
-        <is>
-          <t>お客さん1人がページに来たとき、平均していくら売上になるか</t>
-        </is>
-      </c>
-      <c r="C3" s="72" t="n"/>
-      <c r="D3" s="72" t="n"/>
-      <c r="E3" s="72" t="n"/>
+          <t>用語解説（お店にたとえた、やさしい版）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="73" t="inlineStr">
+        <is>
+          <t>用語</t>
+        </is>
+      </c>
+      <c r="B3" s="73" t="inlineStr">
+        <is>
+          <t>お店で言うと</t>
+        </is>
+      </c>
+      <c r="C3" s="73" t="inlineStr">
+        <is>
+          <t>意味</t>
+        </is>
+      </c>
+      <c r="D3" s="73" t="inlineStr">
+        <is>
+          <t>この店の数字(7月実績)</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="70" t="inlineStr">
-        <is>
-          <t>計算式</t>
+      <c r="A4" s="84" t="inlineStr">
+        <is>
+          <t>アクセス数</t>
         </is>
       </c>
       <c r="B4" s="71" t="inlineStr">
         <is>
-          <t>1アクセス価値 ＝ 転換率 × 客単価</t>
-        </is>
-      </c>
-      <c r="C4" s="72" t="n"/>
-      <c r="D4" s="72" t="n"/>
-      <c r="E4" s="72" t="n"/>
+          <t>お店に入ってきた人数</t>
+        </is>
+      </c>
+      <c r="C4" s="71" t="inlineStr">
+        <is>
+          <t>ページを見に来た人の数（買わない人も含む）</t>
+        </is>
+      </c>
+      <c r="D4" s="71" t="inlineStr">
+        <is>
+          <t>かぶり日 約4.2万人/日</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="70" t="inlineStr">
-        <is>
-          <t>例（かぶり日・7月実績）</t>
+      <c r="A5" s="84" t="inlineStr">
+        <is>
+          <t>転換率</t>
         </is>
       </c>
       <c r="B5" s="71" t="inlineStr">
         <is>
-          <t>転換率0.73% × 客単価¥13,048 ≒ ¥95。1,000人来たら約7人が買い、売上約¥95,000 → 1人あたり¥95</t>
-        </is>
-      </c>
-      <c r="C5" s="72" t="n"/>
-      <c r="D5" s="72" t="n"/>
-      <c r="E5" s="72" t="n"/>
+          <t>入った人のうち買った人の割合</t>
+        </is>
+      </c>
+      <c r="C5" s="71" t="inlineStr">
+        <is>
+          <t>100人入店して1人買えば1%</t>
+        </is>
+      </c>
+      <c r="D5" s="71" t="inlineStr">
+        <is>
+          <t>かぶり日0.73%＝1,000人中7人</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="70" t="inlineStr">
-        <is>
-          <t>使い方①（広告判断）</t>
+      <c r="A6" s="84" t="inlineStr">
+        <is>
+          <t>客単価</t>
         </is>
       </c>
       <c r="B6" s="71" t="inlineStr">
         <is>
-          <t>アクセス単価と比べる。¥10で1人連れてきて、その日の価値が¥95なら9.5倍で返る計算</t>
-        </is>
-      </c>
-      <c r="C6" s="72" t="n"/>
-      <c r="D6" s="72" t="n"/>
-      <c r="E6" s="72" t="n"/>
+          <t>買った人1人の平均支払額</t>
+        </is>
+      </c>
+      <c r="C6" s="71" t="inlineStr">
+        <is>
+          <t>レジ1回の平均金額</t>
+        </is>
+      </c>
+      <c r="D6" s="71" t="inlineStr">
+        <is>
+          <t>かぶり日¥13,048</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="70" t="inlineStr">
-        <is>
-          <t>使い方②（増額試算）</t>
-        </is>
-      </c>
-      <c r="B7" s="71" t="inlineStr">
-        <is>
-          <t>追加売上 ＝ 増やすアクセス数 × 1アクセス価値。転換率×0.8のシナリオは価値を2割引きで見積もったもの</t>
-        </is>
-      </c>
-      <c r="C7" s="72" t="n"/>
-      <c r="D7" s="72" t="n"/>
-      <c r="E7" s="72" t="n"/>
+      <c r="A7" s="85" t="inlineStr">
+        <is>
+          <t>1アクセス価値</t>
+        </is>
+      </c>
+      <c r="B7" s="86" t="inlineStr">
+        <is>
+          <t>入店客1人あたりの平均売上</t>
+        </is>
+      </c>
+      <c r="C7" s="86" t="inlineStr">
+        <is>
+          <t>転換率×客単価。1人来店するたび平均いくら売れるか</t>
+        </is>
+      </c>
+      <c r="D7" s="86" t="inlineStr">
+        <is>
+          <t>かぶり日¥95／平日¥41</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="70" t="inlineStr">
-        <is>
-          <t>★アクセス単価の統一前提</t>
-        </is>
-      </c>
-      <c r="B8" s="71" t="inlineStr">
-        <is>
-          <t>スーツケース ¥10/アクセス ／ ハンディファン ¥8/アクセス（社長指定・全シート共通）</t>
-        </is>
-      </c>
-      <c r="C8" s="72" t="n"/>
-      <c r="D8" s="72" t="n"/>
-      <c r="E8" s="72" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="31" t="inlineStr">
-        <is>
-          <t>セグメント別 1アクセス価値（7月公式実績・店舗全体）</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="73" t="inlineStr">
-        <is>
-          <t>区分</t>
-        </is>
-      </c>
-      <c r="B11" s="73" t="inlineStr">
-        <is>
-          <t>1アクセス価値</t>
-        </is>
-      </c>
-      <c r="C11" s="73" t="inlineStr">
-        <is>
-          <t>SC単価</t>
-        </is>
-      </c>
-      <c r="D11" s="73" t="inlineStr">
+      <c r="A8" s="85" t="inlineStr">
+        <is>
+          <t>アクセス単価</t>
+        </is>
+      </c>
+      <c r="B8" s="86" t="inlineStr">
+        <is>
+          <t>1人を連れてくるチラシ代</t>
+        </is>
+      </c>
+      <c r="C8" s="86" t="inlineStr">
+        <is>
+          <t>広告費÷アクセス数</t>
+        </is>
+      </c>
+      <c r="D8" s="86" t="inlineStr">
+        <is>
+          <t>スーツケース¥10／ファン¥8（統一）</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="84" t="inlineStr">
         <is>
           <t>倍率</t>
         </is>
       </c>
-      <c r="E11" s="73" t="inlineStr">
-        <is>
-          <t>読み方</t>
+      <c r="B9" s="71" t="inlineStr">
+        <is>
+          <t>チラシ代の何倍売れるか</t>
+        </is>
+      </c>
+      <c r="C9" s="71" t="inlineStr">
+        <is>
+          <t>1アクセス価値÷アクセス単価</t>
+        </is>
+      </c>
+      <c r="D9" s="71" t="inlineStr">
+        <is>
+          <t>かぶり日9.5倍／平日4.1倍</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="84" t="inlineStr">
+        <is>
+          <t>かぶり日</t>
+        </is>
+      </c>
+      <c r="B10" s="71" t="inlineStr">
+        <is>
+          <t>特売日が2つ重なった日</t>
+        </is>
+      </c>
+      <c r="C10" s="71" t="inlineStr">
+        <is>
+          <t>お買い物マラソン×5と0のつく日</t>
+        </is>
+      </c>
+      <c r="D10" s="71" t="inlineStr">
+        <is>
+          <t>8/5・8/10・8/25</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="43" t="inlineStr">
-        <is>
-          <t>かぶり日（イベント×5と0）</t>
-        </is>
-      </c>
-      <c r="B12" s="44" t="n">
-        <v>95</v>
-      </c>
-      <c r="C12" s="44" t="n">
-        <v>10</v>
-      </c>
-      <c r="D12" s="74" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="E12" s="75" t="inlineStr">
-        <is>
-          <t>¥10仕入→¥95売上。最優先で広告を張る日</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="47" t="inlineStr">
-        <is>
-          <t>ワンダフルデー</t>
-        </is>
-      </c>
-      <c r="B13" s="48" t="n">
-        <v>94</v>
-      </c>
-      <c r="C13" s="48" t="n">
-        <v>10</v>
-      </c>
-      <c r="D13" s="76" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="E13" s="77" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="45" t="inlineStr">
-        <is>
-          <t>5と0のつく日（単独）</t>
-        </is>
-      </c>
-      <c r="B14" s="46" t="n">
-        <v>61</v>
-      </c>
-      <c r="C14" s="46" t="n">
-        <v>10</v>
-      </c>
-      <c r="D14" s="78" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="E14" s="79" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="49" t="inlineStr">
-        <is>
-          <t>マラソン通常</t>
-        </is>
-      </c>
-      <c r="B15" s="50" t="n">
-        <v>46</v>
-      </c>
-      <c r="C15" s="50" t="n">
-        <v>10</v>
-      </c>
-      <c r="D15" s="80" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="E15" s="81" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="51" t="inlineStr">
-        <is>
-          <t>平日</t>
-        </is>
-      </c>
-      <c r="B16" s="52" t="n">
-        <v>41</v>
-      </c>
-      <c r="C16" s="52" t="n">
-        <v>10</v>
-      </c>
-      <c r="D16" s="82" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="E16" s="83" t="inlineStr">
-        <is>
-          <t>それでも4.1倍。広告を切らない理由</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>※スーツケースのみの価値：平日¥45／かぶり日¥110。ハンディファンの広告費は¥8/アクセス（据え置き）。</t>
-        </is>
-      </c>
+      <c r="A12" s="70" t="inlineStr">
+        <is>
+          <t>商売の流れ</t>
+        </is>
+      </c>
+      <c r="B12" s="71" t="inlineStr">
+        <is>
+          <t>広告費を払う(¥10で1人) → お客さんが来る(アクセス) → 一部が買う(転換率) → 売上(客単価)</t>
+        </is>
+      </c>
+      <c r="C12" s="72" t="n"/>
+      <c r="D12" s="72" t="n"/>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="70" t="inlineStr">
+        <is>
+          <t>かぶり日の例</t>
+        </is>
+      </c>
+      <c r="B13" s="71" t="inlineStr">
+        <is>
+          <t>¥10×1,000人=広告費¥1万 → 1,000人来店 → 7人購入 → 売上¥95,000（＝9.5倍）。平日は同じ¥1万で¥41,000（4.1倍）</t>
+        </is>
+      </c>
+      <c r="C13" s="72" t="n"/>
+      <c r="D13" s="72" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="B8:E8"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="B6:E6"/>
-    <mergeCell ref="B7:E7"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="B5:E5"/>
+  <mergeCells count="2">
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="B13:D13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
